--- a/SeleniumTests/TestDataFolder/TemplateEditorTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/TemplateEditorTestDataValid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6BEB0D-BF0C-4DFA-A4D6-CC898F0DEA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5234B0-1D9F-49D7-AB9A-037AEBDABE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4728" yWindow="2748" windowWidth="18408" windowHeight="10920" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37875" yWindow="2490" windowWidth="17280" windowHeight="9960" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DocumentTemplateTestData" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
   <si>
     <t>Template Name</t>
   </si>
@@ -154,30 +154,12 @@
     <t>DCT_000010</t>
   </si>
   <si>
-    <t>All Information Testing</t>
-  </si>
-  <si>
     <t>All Template (Active/Inactive)</t>
   </si>
   <si>
-    <t>Complete Template testing 6</t>
-  </si>
-  <si>
-    <t>All Information Testing 6</t>
-  </si>
-  <si>
-    <t>Template Description 6</t>
-  </si>
-  <si>
     <t>Complete Template</t>
   </si>
   <si>
-    <t>All Information 7</t>
-  </si>
-  <si>
-    <t>Complete Template testing 7</t>
-  </si>
-  <si>
     <t>All Report edited 6</t>
   </si>
   <si>
@@ -187,13 +169,37 @@
     <t>RPT_000004</t>
   </si>
   <si>
-    <t>Clone3</t>
-  </si>
-  <si>
-    <t>RPT_000009</t>
-  </si>
-  <si>
     <t>All Information update clone 3</t>
+  </si>
+  <si>
+    <t>RPT_000029</t>
+  </si>
+  <si>
+    <t>test 7</t>
+  </si>
+  <si>
+    <t>Select All Template (All)</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>Complete Template testing 17</t>
+  </si>
+  <si>
+    <t>All Information Testing 17</t>
+  </si>
+  <si>
+    <t>Complete Template testing 20</t>
+  </si>
+  <si>
+    <t>All Information 20</t>
+  </si>
+  <si>
+    <t>All Information Testing 21</t>
+  </si>
+  <si>
+    <t>Template Description 21</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
         <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
@@ -587,19 +593,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -631,10 +634,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -667,7 +670,7 @@
         <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
@@ -675,13 +678,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -896,7 +899,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -940,10 +943,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
@@ -987,10 +990,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
